--- a/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_14_19_nov.xlsx
+++ b/InfoTabloServer/bin/Debug/net6.0/Raspisanie/_14_19_nov.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="487">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="504">
   <x:si>
     <x:t>УТВЕРЖДАЮ</x:t>
   </x:si>
@@ -2114,24 +2114,87 @@
     <x:t>Суббота</x:t>
   </x:si>
   <x:si>
+    <x:t>1. Иностранный язык Сергеева Н.В. 
+Основной корпус-Аудитория 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Литература Мякушина И.В. 
+Производственный корпус-Аудитория 45</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Физическая культура 
+Никитина В.Л. 
+-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Иностранный язык 
+Цибарт П.А. 
+Производственный корпус-Аудитория 41</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-Аудитория 124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Основы алгоритмизации и программирования 
+Селищева О.И. 
+Основной корпус-Аудитория 403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.11.01 Технология разработки и защиты баз данных 
+Лукьяненко О.В. 
+Основной корпус-Аудитория 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Иностранный язык Сергеева Н.В. 
+Основной корпус-Аудитория 302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Литература Лыжина Л.А. 
+Производственный корпус-Аудитория 25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Математика 
+Литвиненко О.Д. 
+Производственный корпус-Аудитория 27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. Основы алгоритмизации и программирования 
+Балакин О.Д. 
+Основной корпус-Аудитория 407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК.04.01 Внедрение и поддержка компьютерных систем 
+Андреева Л.В. 
+Основной корпус-Аудитория 308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>МДК 05.01 Проектирование и дизайн информационных систем 
+Бушуева О.О. 
+Основной корпус-Аудитория 306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Литература Лыжина Л.А. 
+Производственный корпус-Аудитория 25</x:t>
+  </x:si>
+  <x:si>
     <x:t>Иностранный язык 
 Сергеева Н.В. 
 Основной корпус-Аудитория 302</x:t>
   </x:si>
   <x:si>
-    <x:t>Иностранный язык 
-Цибарт П.А. 
-Производственный корпус-Аудитория 41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Основы алгоритмизации и программирования 
-Селищева О.И. 
-Основной корпус-Аудитория 403</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК.11.01 Технология разработки и защиты баз данных 
-Лукьяненко О.В. 
-Основной корпус-Аудитория 404</x:t>
+    <x:t>3. Математика Жеколдина Р.Р. 
+Производственный корпус-Аудитория 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-Аудитория 124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. МДК 01.01 Организация безналичных расчетов Лопатина М.М. 
+Производственный корпус-Аудитория 37</x:t>
   </x:si>
   <x:si>
     <x:t>Основы алгоритмизации и программирования 
@@ -2139,21 +2202,6 @@
 Основной корпус-Аудитория 407</x:t>
   </x:si>
   <x:si>
-    <x:t>МДК.04.01 Внедрение и поддержка компьютерных систем 
-Андреева Л.В. 
-Основной корпус-Аудитория 308</x:t>
-  </x:si>
-  <x:si>
-    <x:t>МДК 05.01 Проектирование и дизайн информационных систем 
-Бушуева О.О. 
-Основной корпус-Аудитория 306</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Элементы высшей математики 
-Игликова А.Н. 
-Производственный корпус-Аудитория 124</x:t>
-  </x:si>
-  <x:si>
     <x:t>Иностранный язык в профессиональной деятельности 
 Цибарт П.А. 
 Производственный корпус-Аудитория 41</x:t>
@@ -2172,6 +2220,25 @@
     <x:t>ДОП (Кисленко М.А.) 107</x:t>
   </x:si>
   <x:si>
+    <x:t>4. Математика Жеколдина Р.Р. 
+Производственный корпус-Аудитория 28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-Аудитория 125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Физическая культура 
+Новиков Р.Е. 
+-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. Элементы высшей математики 
+Синельникова К.С. 
+Производственный корпус-Аудитория 21</x:t>
+  </x:si>
+  <x:si>
     <x:t>МДК 02.02  Учет кредитых операций банка 
 Крамаренко Т.С. 
 Производственный корпус-Аудитория 24</x:t>
@@ -2185,6 +2252,16 @@
     <x:t>МДК.01.02 Поддержка и тестирование программных модулей  
 Малышев А.О. 
 Основной корпус-Аудитория 410</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Элементы высшей математики 
+Игликова А.Н. 
+Производственный корпус-Аудитория 125</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. Основы бухгалтерского учета 
+Саликова М.А. 
+Производственный корпус-Аудитория 33</x:t>
   </x:si>
   <x:si>
     <x:t>Информационные технологии в профессиональной деятельности 
@@ -3683,6 +3760,15 @@
       <x:c r="AD2" s="31" t="s"/>
       <x:c r="AE2" s="31" t="s"/>
       <x:c r="AF2" s="31" t="s"/>
+      <x:c r="AG2" s="29" t="s"/>
+      <x:c r="AH2" s="29" t="s"/>
+      <x:c r="AI2" s="29" t="s"/>
+      <x:c r="AJ2" s="29" t="s"/>
+      <x:c r="AK2" s="29" t="s"/>
+      <x:c r="AL2" s="29" t="s"/>
+      <x:c r="AM2" s="29" t="s"/>
+      <x:c r="AN2" s="29" t="s"/>
+      <x:c r="AO2" s="29" t="s"/>
       <x:c r="AP2" s="29" t="s"/>
       <x:c r="AQ2" s="29" t="s"/>
       <x:c r="AR2" s="29" t="s"/>
@@ -3740,6 +3826,15 @@
       <x:c r="AD3" s="34" t="s"/>
       <x:c r="AE3" s="34" t="s"/>
       <x:c r="AF3" s="34" t="s"/>
+      <x:c r="AG3" s="29" t="s"/>
+      <x:c r="AH3" s="29" t="s"/>
+      <x:c r="AI3" s="29" t="s"/>
+      <x:c r="AJ3" s="29" t="s"/>
+      <x:c r="AK3" s="29" t="s"/>
+      <x:c r="AL3" s="29" t="s"/>
+      <x:c r="AM3" s="29" t="s"/>
+      <x:c r="AN3" s="29" t="s"/>
+      <x:c r="AO3" s="29" t="s"/>
       <x:c r="AP3" s="29" t="s"/>
       <x:c r="AQ3" s="29" t="s"/>
       <x:c r="AR3" s="29" t="s"/>
@@ -3795,6 +3890,15 @@
       <x:c r="AD4" s="34" t="s"/>
       <x:c r="AE4" s="34" t="s"/>
       <x:c r="AF4" s="34" t="s"/>
+      <x:c r="AG4" s="29" t="s"/>
+      <x:c r="AH4" s="29" t="s"/>
+      <x:c r="AI4" s="29" t="s"/>
+      <x:c r="AJ4" s="29" t="s"/>
+      <x:c r="AK4" s="29" t="s"/>
+      <x:c r="AL4" s="29" t="s"/>
+      <x:c r="AM4" s="29" t="s"/>
+      <x:c r="AN4" s="29" t="s"/>
+      <x:c r="AO4" s="29" t="s"/>
       <x:c r="AP4" s="29" t="s"/>
       <x:c r="AQ4" s="29" t="s"/>
       <x:c r="AR4" s="29" t="s"/>
@@ -8151,13 +8255,13 @@
         <x:v>251</x:v>
       </x:c>
       <x:c r="D36" s="49" t="s"/>
-      <x:c r="E36" s="49" t="s">
-        <x:v>234</x:v>
+      <x:c r="E36" s="42" t="s">
+        <x:v>214</x:v>
       </x:c>
       <x:c r="F36" s="49" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="G36" s="49" t="s">
+      <x:c r="G36" s="39" t="s">
         <x:v>467</x:v>
       </x:c>
       <x:c r="H36" s="49" t="s"/>
@@ -8170,8 +8274,8 @@
       <x:c r="K36" s="49" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="L36" s="49" t="s">
-        <x:v>209</x:v>
+      <x:c r="L36" s="39" t="s">
+        <x:v>468</x:v>
       </x:c>
       <x:c r="M36" s="49" t="s">
         <x:v>146</x:v>
@@ -8184,35 +8288,39 @@
       <x:c r="Q36" s="49" t="s">
         <x:v>192</x:v>
       </x:c>
-      <x:c r="R36" s="49" t="s"/>
-      <x:c r="S36" s="49" t="s">
-        <x:v>94</x:v>
+      <x:c r="R36" s="42" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="S36" s="39" t="s">
+        <x:v>469</x:v>
       </x:c>
       <x:c r="T36" s="49" t="s">
-        <x:v>468</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="U36" s="49" t="s"/>
-      <x:c r="V36" s="49" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="W36" s="49" t="s">
-        <x:v>439</x:v>
+      <x:c r="V36" s="39" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="W36" s="0" t="s">
+        <x:v>214</x:v>
       </x:c>
       <x:c r="X36" s="49" t="s">
         <x:v>311</x:v>
       </x:c>
       <x:c r="Y36" s="49" t="s"/>
-      <x:c r="Z36" s="49" t="s"/>
+      <x:c r="Z36" s="42" t="s">
+        <x:v>90</x:v>
+      </x:c>
       <x:c r="AA36" s="49" t="s"/>
       <x:c r="AB36" s="49" t="s">
         <x:v>159</x:v>
       </x:c>
       <x:c r="AC36" s="49" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="AD36" s="49" t="s"/>
-      <x:c r="AE36" s="49" t="s">
-        <x:v>126</x:v>
+      <x:c r="AE36" s="39" t="s">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="AF36" s="49" t="s">
         <x:v>438</x:v>
@@ -8249,7 +8357,7 @@
       <x:c r="AT36" s="49" t="s"/>
       <x:c r="AU36" s="49" t="s"/>
       <x:c r="AV36" s="49" t="s">
-        <x:v>470</x:v>
+        <x:v>473</x:v>
       </x:c>
       <x:c r="AW36" s="49" t="s"/>
       <x:c r="AX36" s="49" t="s"/>
@@ -8281,14 +8389,14 @@
       <x:c r="D37" s="49" t="s">
         <x:v>323</x:v>
       </x:c>
-      <x:c r="E37" s="49" t="s">
-        <x:v>467</x:v>
+      <x:c r="E37" s="39" t="s">
+        <x:v>474</x:v>
       </x:c>
       <x:c r="F37" s="49" t="s">
         <x:v>310</x:v>
       </x:c>
-      <x:c r="G37" s="49" t="s">
-        <x:v>116</x:v>
+      <x:c r="G37" s="39" t="s">
+        <x:v>475</x:v>
       </x:c>
       <x:c r="H37" s="49" t="s">
         <x:v>251</x:v>
@@ -8303,7 +8411,7 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="L37" s="49" t="s">
-        <x:v>234</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="M37" s="49" t="s">
         <x:v>108</x:v>
@@ -8318,21 +8426,23 @@
       <x:c r="Q37" s="49" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="R37" s="49" t="s"/>
-      <x:c r="S37" s="49" t="s">
-        <x:v>146</x:v>
+      <x:c r="R37" s="42" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="S37" s="39" t="s">
+        <x:v>476</x:v>
       </x:c>
       <x:c r="T37" s="49" t="s">
         <x:v>309</x:v>
       </x:c>
       <x:c r="U37" s="49" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="V37" s="49" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="W37" s="49" t="s">
-        <x:v>319</x:v>
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="V37" s="39" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="W37" s="42" t="s">
+        <x:v>226</x:v>
       </x:c>
       <x:c r="X37" s="49" t="s">
         <x:v>94</x:v>
@@ -8340,9 +8450,11 @@
       <x:c r="Y37" s="49" t="s">
         <x:v>257</x:v>
       </x:c>
-      <x:c r="Z37" s="49" t="s"/>
+      <x:c r="Z37" s="42" t="s">
+        <x:v>226</x:v>
+      </x:c>
       <x:c r="AA37" s="49" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="AB37" s="49" t="s">
         <x:v>268</x:v>
@@ -8353,11 +8465,11 @@
       <x:c r="AD37" s="49" t="s">
         <x:v>159</x:v>
       </x:c>
-      <x:c r="AE37" s="49" t="s">
-        <x:v>471</x:v>
+      <x:c r="AE37" s="39" t="s">
+        <x:v>477</x:v>
       </x:c>
       <x:c r="AF37" s="49" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="AG37" s="49" t="s">
         <x:v>102</x:v>
@@ -8404,7 +8516,7 @@
       </x:c>
       <x:c r="BB37" s="49" t="s"/>
       <x:c r="BC37" s="49" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="BD37" s="49" t="s"/>
       <x:c r="BE37" s="49" t="s"/>
@@ -8431,14 +8543,14 @@
       <x:c r="D38" s="49" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="E38" s="49" t="s">
-        <x:v>116</x:v>
+      <x:c r="E38" s="39" t="s">
+        <x:v>480</x:v>
       </x:c>
       <x:c r="F38" s="49" t="s">
-        <x:v>467</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="G38" s="49" t="s">
-        <x:v>234</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H38" s="49" t="s">
         <x:v>74</x:v>
@@ -8452,7 +8564,9 @@
       <x:c r="K38" s="49" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="L38" s="49" t="s"/>
+      <x:c r="L38" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="M38" s="49" t="s">
         <x:v>192</x:v>
       </x:c>
@@ -8466,11 +8580,11 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="Q38" s="49" t="s"/>
-      <x:c r="R38" s="49" t="s">
-        <x:v>425</x:v>
+      <x:c r="R38" s="39" t="s">
+        <x:v>482</x:v>
       </x:c>
       <x:c r="S38" s="49" t="s">
-        <x:v>456</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="T38" s="49" t="s">
         <x:v>236</x:v>
@@ -8478,11 +8592,11 @@
       <x:c r="U38" s="49" t="s">
         <x:v>309</x:v>
       </x:c>
-      <x:c r="V38" s="49" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="W38" s="49" t="s">
-        <x:v>152</x:v>
+      <x:c r="V38" s="39" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="W38" s="39" t="s">
+        <x:v>484</x:v>
       </x:c>
       <x:c r="X38" s="49" t="s">
         <x:v>257</x:v>
@@ -8490,29 +8604,29 @@
       <x:c r="Y38" s="49" t="s">
         <x:v>162</x:v>
       </x:c>
-      <x:c r="Z38" s="49" t="s">
-        <x:v>319</x:v>
+      <x:c r="Z38" s="42" t="s">
+        <x:v>390</x:v>
       </x:c>
       <x:c r="AA38" s="49" t="s">
         <x:v>159</x:v>
       </x:c>
       <x:c r="AB38" s="49" t="s">
-        <x:v>469</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="AC38" s="49" t="s">
         <x:v>165</x:v>
       </x:c>
       <x:c r="AD38" s="49" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="AE38" s="49" t="s">
-        <x:v>126</x:v>
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="AE38" s="39" t="s">
+        <x:v>259</x:v>
       </x:c>
       <x:c r="AF38" s="49" t="s">
         <x:v>102</x:v>
       </x:c>
       <x:c r="AG38" s="49" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="AH38" s="49" t="s"/>
       <x:c r="AI38" s="49" t="s">
@@ -8545,20 +8659,20 @@
       </x:c>
       <x:c r="AW38" s="49" t="s"/>
       <x:c r="AX38" s="49" t="s">
-        <x:v>475</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="AY38" s="49" t="s">
-        <x:v>476</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="AZ38" s="49" t="s">
-        <x:v>477</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="BA38" s="49" t="s">
         <x:v>415</x:v>
       </x:c>
       <x:c r="BB38" s="49" t="s"/>
       <x:c r="BC38" s="49" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="BD38" s="49" t="s"/>
       <x:c r="BE38" s="49" t="s">
@@ -8572,7 +8686,7 @@
         <x:v>268</x:v>
       </x:c>
       <x:c r="BI38" s="50" t="s">
-        <x:v>478</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="BJ38" s="49" t="s">
         <x:v>187</x:v>
@@ -8587,37 +8701,49 @@
       <x:c r="D39" s="49" t="s">
         <x:v>209</x:v>
       </x:c>
-      <x:c r="E39" s="49" t="s"/>
+      <x:c r="E39" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="F39" s="49" t="s"/>
-      <x:c r="G39" s="49" t="s"/>
+      <x:c r="G39" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="H39" s="49" t="s"/>
       <x:c r="I39" s="49" t="s"/>
       <x:c r="J39" s="49" t="s"/>
       <x:c r="K39" s="49" t="s"/>
-      <x:c r="L39" s="49" t="s"/>
+      <x:c r="L39" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="M39" s="49" t="s"/>
       <x:c r="N39" s="49" t="s">
         <x:v>146</x:v>
       </x:c>
       <x:c r="O39" s="49" t="s">
-        <x:v>467</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="P39" s="49" t="s"/>
       <x:c r="Q39" s="49" t="s"/>
-      <x:c r="R39" s="49" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="S39" s="49" t="s"/>
+      <x:c r="R39" s="39" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="S39" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="T39" s="49" t="s"/>
       <x:c r="U39" s="49" t="s"/>
-      <x:c r="V39" s="49" t="s"/>
-      <x:c r="W39" s="49" t="s"/>
+      <x:c r="V39" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="W39" s="39" t="s">
+        <x:v>491</x:v>
+      </x:c>
       <x:c r="X39" s="49" t="s"/>
       <x:c r="Y39" s="49" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="Z39" s="49" t="s">
-        <x:v>74</x:v>
+      <x:c r="Z39" s="39" t="s">
+        <x:v>492</x:v>
       </x:c>
       <x:c r="AA39" s="49" t="s">
         <x:v>312</x:v>
@@ -8625,7 +8751,9 @@
       <x:c r="AB39" s="49" t="s"/>
       <x:c r="AC39" s="49" t="s"/>
       <x:c r="AD39" s="49" t="s"/>
-      <x:c r="AE39" s="49" t="s"/>
+      <x:c r="AE39" s="39" t="s">
+        <x:v>493</x:v>
+      </x:c>
       <x:c r="AF39" s="49" t="s"/>
       <x:c r="AG39" s="49" t="s"/>
       <x:c r="AH39" s="49" t="s"/>
@@ -8634,7 +8762,7 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="AK39" s="49" t="s">
-        <x:v>479</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="AL39" s="49" t="s">
         <x:v>130</x:v>
@@ -8664,7 +8792,7 @@
         <x:v>460</x:v>
       </x:c>
       <x:c r="AY39" s="49" t="s">
-        <x:v>476</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="AZ39" s="49" t="s">
         <x:v>287</x:v>
@@ -8679,20 +8807,20 @@
         <x:v>342</x:v>
       </x:c>
       <x:c r="BD39" s="49" t="s">
-        <x:v>480</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="BE39" s="49" t="s">
         <x:v>350</x:v>
       </x:c>
       <x:c r="BF39" s="49" t="s">
-        <x:v>481</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="BG39" s="49" t="s">
         <x:v>300</x:v>
       </x:c>
       <x:c r="BH39" s="49" t="s"/>
       <x:c r="BI39" s="50" t="s">
-        <x:v>478</x:v>
+        <x:v>489</x:v>
       </x:c>
       <x:c r="BJ39" s="49" t="s"/>
     </x:row>
@@ -8705,37 +8833,51 @@
       <x:c r="D40" s="49" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="E40" s="49" t="s"/>
+      <x:c r="E40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="F40" s="49" t="s"/>
-      <x:c r="G40" s="49" t="s"/>
+      <x:c r="G40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="H40" s="49" t="s"/>
       <x:c r="I40" s="49" t="s"/>
       <x:c r="J40" s="49" t="s"/>
       <x:c r="K40" s="49" t="s"/>
-      <x:c r="L40" s="49" t="s"/>
+      <x:c r="L40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="M40" s="49" t="s"/>
       <x:c r="N40" s="49" t="s"/>
       <x:c r="O40" s="49" t="s"/>
       <x:c r="P40" s="49" t="s"/>
       <x:c r="Q40" s="49" t="s"/>
       <x:c r="R40" s="49" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="S40" s="49" t="s"/>
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="S40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="T40" s="49" t="s"/>
       <x:c r="U40" s="49" t="s"/>
-      <x:c r="V40" s="49" t="s"/>
-      <x:c r="W40" s="49" t="s"/>
+      <x:c r="V40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="W40" s="39" t="s">
+        <x:v>497</x:v>
+      </x:c>
       <x:c r="X40" s="49" t="s"/>
       <x:c r="Y40" s="49" t="s"/>
-      <x:c r="Z40" s="49" t="s">
-        <x:v>216</x:v>
+      <x:c r="Z40" s="39" t="s">
+        <x:v>498</x:v>
       </x:c>
       <x:c r="AA40" s="49" t="s"/>
       <x:c r="AB40" s="49" t="s"/>
       <x:c r="AC40" s="49" t="s"/>
       <x:c r="AD40" s="49" t="s"/>
-      <x:c r="AE40" s="49" t="s"/>
+      <x:c r="AE40" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="AF40" s="49" t="s"/>
       <x:c r="AG40" s="49" t="s"/>
       <x:c r="AH40" s="49" t="s"/>
@@ -8744,7 +8886,7 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="AK40" s="49" t="s">
-        <x:v>482</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="AL40" s="49" t="s">
         <x:v>98</x:v>
@@ -8770,7 +8912,7 @@
       </x:c>
       <x:c r="AX40" s="49" t="s"/>
       <x:c r="AY40" s="49" t="s">
-        <x:v>483</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="AZ40" s="49" t="s">
         <x:v>287</x:v>
@@ -8790,7 +8932,7 @@
       </x:c>
       <x:c r="BF40" s="49" t="s"/>
       <x:c r="BG40" s="49" t="s">
-        <x:v>484</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="BH40" s="49" t="s"/>
       <x:c r="BI40" s="49" t="s">
@@ -8805,41 +8947,57 @@
       </x:c>
       <x:c r="C41" s="49" t="s"/>
       <x:c r="D41" s="49" t="s"/>
-      <x:c r="E41" s="49" t="s"/>
+      <x:c r="E41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="F41" s="49" t="s"/>
-      <x:c r="G41" s="49" t="s"/>
+      <x:c r="G41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="H41" s="49" t="s"/>
       <x:c r="I41" s="49" t="s"/>
       <x:c r="J41" s="49" t="s"/>
       <x:c r="K41" s="49" t="s"/>
-      <x:c r="L41" s="49" t="s"/>
+      <x:c r="L41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="M41" s="49" t="s"/>
       <x:c r="N41" s="49" t="s"/>
       <x:c r="O41" s="49" t="s"/>
       <x:c r="P41" s="49" t="s"/>
       <x:c r="Q41" s="49" t="s"/>
       <x:c r="R41" s="49" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="S41" s="49" t="s"/>
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="S41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="T41" s="49" t="s"/>
       <x:c r="U41" s="49" t="s"/>
-      <x:c r="V41" s="49" t="s"/>
-      <x:c r="W41" s="49" t="s"/>
+      <x:c r="V41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="W41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="X41" s="49" t="s"/>
       <x:c r="Y41" s="49" t="s"/>
-      <x:c r="Z41" s="49" t="s"/>
+      <x:c r="Z41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="AA41" s="49" t="s"/>
       <x:c r="AB41" s="49" t="s"/>
       <x:c r="AC41" s="49" t="s"/>
       <x:c r="AD41" s="49" t="s"/>
-      <x:c r="AE41" s="49" t="s"/>
+      <x:c r="AE41" s="49" t="s">
+        <x:v>145</x:v>
+      </x:c>
       <x:c r="AF41" s="49" t="s"/>
       <x:c r="AG41" s="49" t="s"/>
       <x:c r="AH41" s="49" t="s"/>
       <x:c r="AI41" s="49" t="s"/>
       <x:c r="AJ41" s="49" t="s">
-        <x:v>482</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="AK41" s="49" t="s">
         <x:v>164</x:v>
@@ -8866,7 +9024,7 @@
       </x:c>
       <x:c r="AX41" s="49" t="s"/>
       <x:c r="AY41" s="49" t="s">
-        <x:v>485</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="AZ41" s="49" t="s">
         <x:v>287</x:v>
@@ -9003,7 +9161,7 @@
   <x:sheetData>
     <x:row r="5" spans="1:1" ht="23.25" customHeight="1">
       <x:c r="A5" s="56" t="s">
-        <x:v>486</x:v>
+        <x:v>503</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
